--- a/فورم المشاركين.xlsx
+++ b/فورم المشاركين.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mo7am\OneDrive\Work\EOC System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dc29ec3854233ba7/Work/EOC System/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF64C2F-9AB5-4F42-AB67-52958A3EB76D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{0DAC1C31-6DF0-466A-AD70-1AEEE946F95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9EA02A0E-0280-4C4D-94E3-E11AD9CBEBC1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C1A66B62-FDA8-44DD-934B-61AB85F6D0A5}"/>
   </bookViews>
@@ -194,6 +194,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -559,15 +563,15 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1DECAF98-6A2E-45D1-9AFC-B3929D94CDF0}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0F535401-82A1-4D25-822C-3FADDB1047EF}">
           <x14:formula1>
-            <xm:f>DV!A1:A2</xm:f>
+            <xm:f>DV!$A$1:$A$2</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A200</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BB4D3DA0-FE4B-4FA4-B92E-393E9FA68C68}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CFB583AC-8468-4BA1-BAF6-68018EA90F57}">
           <x14:formula1>
-            <xm:f>DV!B1:B27</xm:f>
+            <xm:f>DV!$B$1:$B$27</xm:f>
           </x14:formula1>
           <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
